--- a/InsectAI CRediT register.xlsx
+++ b/InsectAI CRediT register.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://naturalhistorymuseum.sharepoint.com/sites/EducationNatureParkProgramme/Shared Documents/Community Science incl digital tools/5. Research planning and data analysis/Insect AI COST Action/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{9805CE59-76B2-4068-B5DB-F15CA8DEEF50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D0307C23-FAFD-4C1E-9E54-C11C92E57712}"/>
+  <xr:revisionPtr revIDLastSave="64" documentId="13_ncr:1_{9805CE59-76B2-4068-B5DB-F15CA8DEEF50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{71AFAC39-AA12-4299-9145-34B110E1C287}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="352" xr2:uid="{4C054703-C80A-4328-B0BE-C3D095480D7D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="352" activeTab="1" xr2:uid="{4C054703-C80A-4328-B0BE-C3D095480D7D}"/>
   </bookViews>
   <sheets>
     <sheet name="CRediT Definitions" sheetId="3" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="49">
   <si>
     <t>Conceptualization</t>
   </si>
@@ -144,18 +144,12 @@
     <t>InsectAI COST Action CRediT Contributor Register</t>
   </si>
   <si>
-    <t>Role(s)</t>
-  </si>
-  <si>
     <t>Institution</t>
   </si>
   <si>
     <t>If you wish to be credited for your work please include your details in the contributors sheet. Your data will be kept solely for attribution and kept in accordance with the InsectAI Privacy Policy which can be viewed here: https://insectai.eu/privacy-policy/</t>
   </si>
   <si>
-    <t>Victoria BURTON</t>
-  </si>
-  <si>
     <t>Centre for UK Nature, Natural History Museum, Cromwell Road, South Kensington, London, SW7 5BS, UK</t>
   </si>
   <si>
@@ -165,9 +159,6 @@
     <t>Contribution details</t>
   </si>
   <si>
-    <t>First name LAST NAME</t>
-  </si>
-  <si>
     <t>ORCID</t>
   </si>
   <si>
@@ -175,6 +166,30 @@
   </si>
   <si>
     <t>Collated curriculum data, Kit for Kids lead for educational resources</t>
+  </si>
+  <si>
+    <t>LAST NAME</t>
+  </si>
+  <si>
+    <t>First name</t>
+  </si>
+  <si>
+    <t>Victoria</t>
+  </si>
+  <si>
+    <t>BURTON</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Dr</t>
+  </si>
+  <si>
+    <t>Initial(s)</t>
+  </si>
+  <si>
+    <t>J</t>
   </si>
 </sst>
 </file>
@@ -235,18 +250,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment textRotation="90"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -260,9 +269,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -270,14 +276,46 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="90" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -288,6 +326,36 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B8178FF4-D7AA-4EF7-A351-3F823F143BAB}" name="Table3" displayName="Table3" ref="A1:U4" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:U4" xr:uid="{B8178FF4-D7AA-4EF7-A351-3F823F143BAB}"/>
+  <tableColumns count="21">
+    <tableColumn id="1" xr3:uid="{17C15E88-DBE9-40A8-80F1-E1E3228CF3D0}" name="Title"/>
+    <tableColumn id="2" xr3:uid="{748815AD-C68B-4121-9EEE-46385F0AD8FA}" name="First name"/>
+    <tableColumn id="3" xr3:uid="{193212B3-3535-4326-8ADA-C493E45DDEE9}" name="Initial(s)"/>
+    <tableColumn id="4" xr3:uid="{0BB2C581-1231-4E6E-A089-4A876CDCFEF0}" name="LAST NAME"/>
+    <tableColumn id="5" xr3:uid="{DA988D6F-0FF5-412C-B77C-2C394E29B1D0}" name="Institution"/>
+    <tableColumn id="6" xr3:uid="{ED68E5E1-AE15-4C49-931B-F12A06B07F74}" name="ORCID"/>
+    <tableColumn id="7" xr3:uid="{BB2C0F34-A95A-47FA-9019-6D89A8760989}" name="Conceptualization"/>
+    <tableColumn id="8" xr3:uid="{11F80567-E06F-40AC-A0BA-37A6B2AFE0F0}" name="Data curation"/>
+    <tableColumn id="9" xr3:uid="{E9DDBFD9-D0C7-46A4-A5CA-1FEC2E7EDB94}" name="Formal analysis"/>
+    <tableColumn id="10" xr3:uid="{C23DF477-5377-4655-BED1-371132F1E934}" name="Funding acquisition"/>
+    <tableColumn id="11" xr3:uid="{47989D53-2A71-486A-A8B6-35F5E2C7AFC9}" name="Investigation"/>
+    <tableColumn id="12" xr3:uid="{49F328E8-69C0-4FE0-92CB-D85B8FAF789F}" name="Methodology"/>
+    <tableColumn id="13" xr3:uid="{3FC8E9BC-3E1B-45C5-8CCB-3B85D6FA4CBF}" name="Project administration"/>
+    <tableColumn id="14" xr3:uid="{0A36A71A-74A5-4D14-8C3F-E65C6970EEAE}" name="Resources"/>
+    <tableColumn id="15" xr3:uid="{A2C08D77-393B-4599-9241-E8EAAD39C4DC}" name="Software"/>
+    <tableColumn id="16" xr3:uid="{96906931-06E7-466E-9D21-B63D8EA18588}" name="Supervision"/>
+    <tableColumn id="17" xr3:uid="{A6EF63DB-0052-4926-ACBE-FE7518E4BDEA}" name="Validation"/>
+    <tableColumn id="18" xr3:uid="{73B35122-EEEF-4B89-9140-4E5BB08F42FE}" name="Visualization"/>
+    <tableColumn id="19" xr3:uid="{C3BF09A8-0191-4B80-AB71-C91BA7C1528B}" name="Writing – original draft"/>
+    <tableColumn id="20" xr3:uid="{22FE8E87-565A-4FD1-B646-2FBED9642169}" name="Writing – review &amp; editing"/>
+    <tableColumn id="21" xr3:uid="{08BD498B-385E-4E35-870F-9761D8C18B62}" name="Contribution details"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -616,38 +684,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="7" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="8"/>
-      <c r="B4" s="9"/>
+      <c r="A4" s="6"/>
+      <c r="B4" s="7"/>
     </row>
     <row r="5" spans="1:3" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" s="12"/>
+      <c r="A5" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="9"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -655,7 +723,7 @@
       <c r="A8" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="4" t="s">
         <v>16</v>
       </c>
     </row>
@@ -663,7 +731,7 @@
       <c r="A9" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="4" t="s">
         <v>17</v>
       </c>
     </row>
@@ -671,7 +739,7 @@
       <c r="A10" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="4" t="s">
         <v>18</v>
       </c>
     </row>
@@ -679,7 +747,7 @@
       <c r="A11" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -687,7 +755,7 @@
       <c r="A12" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="4" t="s">
         <v>20</v>
       </c>
     </row>
@@ -695,7 +763,7 @@
       <c r="A13" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="4" t="s">
         <v>21</v>
       </c>
     </row>
@@ -703,7 +771,7 @@
       <c r="A14" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="4" t="s">
         <v>22</v>
       </c>
     </row>
@@ -711,7 +779,7 @@
       <c r="A15" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="4" t="s">
         <v>23</v>
       </c>
     </row>
@@ -719,7 +787,7 @@
       <c r="A16" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="4" t="s">
         <v>24</v>
       </c>
     </row>
@@ -727,7 +795,7 @@
       <c r="A17" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="4" t="s">
         <v>25</v>
       </c>
     </row>
@@ -735,7 +803,7 @@
       <c r="A18" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="4" t="s">
         <v>26</v>
       </c>
     </row>
@@ -743,7 +811,7 @@
       <c r="A19" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="4" t="s">
         <v>27</v>
       </c>
     </row>
@@ -751,7 +819,7 @@
       <c r="A20" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="4" t="s">
         <v>28</v>
       </c>
     </row>
@@ -759,7 +827,7 @@
       <c r="A21" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="5" t="s">
         <v>29</v>
       </c>
     </row>
@@ -778,138 +846,125 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D6DC2CA-E426-46ED-A29E-DB1A8DD372C0}">
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:U2"/>
   <sheetFormatPr defaultColWidth="24.36328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="48.90625" style="7" customWidth="1"/>
-    <col min="3" max="3" width="18.6328125" style="7" customWidth="1"/>
-    <col min="4" max="17" width="3.36328125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="55.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="47.08984375" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.90625" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="20" width="5.6328125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="55.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="D1" s="13" t="s">
+    <row r="1" spans="1:21" s="14" customFormat="1" ht="120" x14ac:dyDescent="0.35">
+      <c r="A1" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
-      <c r="Q1" s="13"/>
-    </row>
-    <row r="2" spans="1:18" ht="120" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+      <c r="F1" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="K1" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="N1" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="O1" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="P1" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q1" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="R1" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="S1" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="T1" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="U1" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" ht="29" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2" t="s">
+        <v>36</v>
+      </c>
+      <c r="U2" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" ht="58" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="E3" t="s">
-        <v>38</v>
-      </c>
-      <c r="R3" t="s">
-        <v>43</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="D1:Q1"/>
-  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:T1048576" xr:uid="{0F7D6B94-B467-43FB-8B17-6E55D0BF9CC7}">
+      <formula1>"x"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Contains xmlns="37c47d49-5c3e-4564-83ee-3a7de24ace65" xsi:nil="true"/>
-    <Credit xmlns="37c47d49-5c3e-4564-83ee-3a7de24ace65" xsi:nil="true"/>
-    <What_x0020_is_x0020_your_x0020_name_x003f__x0020__x0028_Note_x003a__x0020_this_x0020_might_x0020_be_x0020_a_x0020_repeat_x0020_question_x0020_if_x0020_the_x0020_form_x0020_already_x0020_asked_x0020_you_x0029_ xmlns="37c47d49-5c3e-4564-83ee-3a7de24ace65" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="37c47d49-5c3e-4564-83ee-3a7de24ace65">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="01a464aa-a786-405b-bb6b-b90e04698418" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A965D94F0762894DBFBF8132F36DD753" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2e5e294aee1e8b15d1ef8ee2be4d20ba">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="01a464aa-a786-405b-bb6b-b90e04698418" xmlns:ns3="37c47d49-5c3e-4564-83ee-3a7de24ace65" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="74ad2e1e60d70087ea82dab5b61f0c8d" ns2:_="" ns3:_="">
     <xsd:import namespace="01a464aa-a786-405b-bb6b-b90e04698418"/>
@@ -1174,26 +1229,30 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Contains xmlns="37c47d49-5c3e-4564-83ee-3a7de24ace65" xsi:nil="true"/>
+    <Credit xmlns="37c47d49-5c3e-4564-83ee-3a7de24ace65" xsi:nil="true"/>
+    <What_x0020_is_x0020_your_x0020_name_x003f__x0020__x0028_Note_x003a__x0020_this_x0020_might_x0020_be_x0020_a_x0020_repeat_x0020_question_x0020_if_x0020_the_x0020_form_x0020_already_x0020_asked_x0020_you_x0029_ xmlns="37c47d49-5c3e-4564-83ee-3a7de24ace65" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="37c47d49-5c3e-4564-83ee-3a7de24ace65">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="01a464aa-a786-405b-bb6b-b90e04698418" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEC2A06E-2947-4083-AF02-58B61C84DFB7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="37c47d49-5c3e-4564-83ee-3a7de24ace65"/>
-    <ds:schemaRef ds:uri="01a464aa-a786-405b-bb6b-b90e04698418"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9AAE77EC-DAF1-4B78-88D6-A3A6D6E12249}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D965612-6479-4472-860E-9EF9F9A3747A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1212,6 +1271,25 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9AAE77EC-DAF1-4B78-88D6-A3A6D6E12249}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEC2A06E-2947-4083-AF02-58B61C84DFB7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="37c47d49-5c3e-4564-83ee-3a7de24ace65"/>
+    <ds:schemaRef ds:uri="01a464aa-a786-405b-bb6b-b90e04698418"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{73a29c01-4e78-437f-a0d4-c8553e1960c1}" enabled="0" method="" siteId="{73a29c01-4e78-437f-a0d4-c8553e1960c1}" removed="1"/>
